--- a/Laboratorio 2/PruebaDeEscritorio.xlsx
+++ b/Laboratorio 2/PruebaDeEscritorio.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Univalle\2026-1\Informatica-1\Laboratorio 2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7361308F-75A8-44D1-960F-805B7786EBB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6568BFA6-C4FF-44BD-9EA3-CB47C0869EDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{2B75A477-A9CF-47B7-B745-DD82E9186679}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="44">
   <si>
     <t>NivelesColesterol</t>
   </si>
@@ -135,12 +135,48 @@
   </si>
   <si>
     <t xml:space="preserve">Ingrese hasta que altura se lleno el recipiente en forma de cilindro: </t>
+  </si>
+  <si>
+    <t>Llamado a funciones</t>
+  </si>
+  <si>
+    <t>colesterolTotal()</t>
+  </si>
+  <si>
+    <t>colesterolHDL()</t>
+  </si>
+  <si>
+    <t>trigliceridos()</t>
+  </si>
+  <si>
+    <t>Salida</t>
+  </si>
+  <si>
+    <t>Intermedio Alto</t>
+  </si>
+  <si>
+    <t>Normal</t>
+  </si>
+  <si>
+    <t>volumenPrisma()</t>
+  </si>
+  <si>
+    <t>volumenCilindro()</t>
+  </si>
+  <si>
+    <t>cantidadLechePrisma()</t>
+  </si>
+  <si>
+    <t>cantidadLecheCilindro()</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="172" formatCode="0.0000000000"/>
+  </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -166,7 +202,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="15">
+  <borders count="16">
     <border>
       <left/>
       <right/>
@@ -190,21 +226,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color indexed="64"/>
       </left>
@@ -374,15 +395,40 @@
         <color indexed="64"/>
       </top>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
@@ -394,9 +440,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="172" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -731,25 +782,26 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8090FB75-1E15-460F-A013-7A93DF31DE48}">
-  <dimension ref="A1:H30"/>
+  <dimension ref="A1:I60"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="90.7109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.5703125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="12.7109375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="13.28515625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="19.7109375" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="22.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="13" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
@@ -765,11 +817,14 @@
       <c r="E2" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="F2" s="4" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G2" s="15" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
         <v>7</v>
       </c>
@@ -779,9 +834,10 @@
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
       <c r="E3" s="2"/>
-      <c r="F3" s="7"/>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F3" s="2"/>
+      <c r="G3" s="7"/>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
         <v>8</v>
       </c>
@@ -791,9 +847,10 @@
       </c>
       <c r="D4" s="1"/>
       <c r="E4" s="1"/>
-      <c r="F4" s="9"/>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F4" s="1"/>
+      <c r="G4" s="9"/>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
         <v>9</v>
       </c>
@@ -803,9 +860,10 @@
         <v>228</v>
       </c>
       <c r="E5" s="1"/>
-      <c r="F5" s="9"/>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F5" s="1"/>
+      <c r="G5" s="9"/>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
         <v>10</v>
       </c>
@@ -815,9 +873,10 @@
       <c r="E6" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="F6" s="9"/>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F6" s="1"/>
+      <c r="G6" s="9"/>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
         <v>11</v>
       </c>
@@ -825,11 +884,12 @@
       <c r="C7" s="1"/>
       <c r="D7" s="1"/>
       <c r="E7" s="1"/>
-      <c r="F7" s="9">
+      <c r="F7" s="1">
         <v>133</v>
       </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G7" s="9"/>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="str">
         <f>_xlfn.CONCAT(B3," sus niveles de colesterol son: ")</f>
         <v xml:space="preserve">Anita López sus niveles de colesterol son: </v>
@@ -838,9 +898,10 @@
       <c r="C8" s="1"/>
       <c r="D8" s="1"/>
       <c r="E8" s="1"/>
-      <c r="F8" s="9"/>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F8" s="1"/>
+      <c r="G8" s="9"/>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="8" t="s">
         <v>15</v>
       </c>
@@ -848,9 +909,12 @@
       <c r="C9" s="1"/>
       <c r="D9" s="1"/>
       <c r="E9" s="1"/>
-      <c r="F9" s="9"/>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F9" s="1"/>
+      <c r="G9" s="9" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="8" t="s">
         <v>16</v>
       </c>
@@ -858,9 +922,12 @@
       <c r="C10" s="1"/>
       <c r="D10" s="1"/>
       <c r="E10" s="1"/>
-      <c r="F10" s="9"/>
-    </row>
-    <row r="11" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F10" s="1"/>
+      <c r="G10" s="9" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="10" t="s">
         <v>17</v>
       </c>
@@ -868,192 +935,536 @@
       <c r="C11" s="11"/>
       <c r="D11" s="11"/>
       <c r="E11" s="11"/>
-      <c r="F11" s="12"/>
-    </row>
-    <row r="12" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="13" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="14" t="s">
+      <c r="F11" s="11"/>
+      <c r="G11" s="12" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="14"/>
+      <c r="B12" s="14"/>
+      <c r="C12" s="14"/>
+      <c r="D12" s="14"/>
+      <c r="E12" s="14"/>
+      <c r="F12" s="14"/>
+      <c r="G12" s="14"/>
+    </row>
+    <row r="13" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="B13" s="14"/>
+      <c r="C13" s="14"/>
+      <c r="D13" s="14"/>
+      <c r="E13" s="14"/>
+      <c r="F13" s="14"/>
+      <c r="G13" s="14"/>
+    </row>
+    <row r="14" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="B14" s="17" t="s">
+        <v>4</v>
+      </c>
+      <c r="C14" s="14"/>
+      <c r="D14" s="14"/>
+      <c r="E14" s="14"/>
+      <c r="F14" s="14"/>
+      <c r="G14" s="14"/>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" s="6"/>
+      <c r="B15" s="18">
+        <v>228</v>
+      </c>
+      <c r="C15" s="14"/>
+      <c r="D15" s="14"/>
+      <c r="E15" s="14"/>
+      <c r="F15" s="14"/>
+      <c r="G15" s="14"/>
+    </row>
+    <row r="16" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="B16" s="12"/>
+      <c r="C16" s="14"/>
+      <c r="D16" s="14"/>
+      <c r="E16" s="14"/>
+      <c r="F16" s="14"/>
+      <c r="G16" s="14"/>
+    </row>
+    <row r="17" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="14"/>
+      <c r="B17" s="14"/>
+      <c r="C17" s="14"/>
+      <c r="D17" s="14"/>
+      <c r="E17" s="14"/>
+      <c r="F17" s="14"/>
+      <c r="G17" s="14"/>
+    </row>
+    <row r="18" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="B18" s="14"/>
+      <c r="C18" s="14"/>
+      <c r="D18" s="14"/>
+      <c r="E18" s="14"/>
+      <c r="F18" s="14"/>
+      <c r="G18" s="14"/>
+    </row>
+    <row r="19" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C19" s="14"/>
+      <c r="D19" s="14"/>
+      <c r="E19" s="14"/>
+      <c r="F19" s="14"/>
+      <c r="G19" s="14"/>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A20" s="6"/>
+      <c r="B20" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C20" s="14"/>
+      <c r="D20" s="14"/>
+      <c r="E20" s="14"/>
+      <c r="F20" s="14"/>
+      <c r="G20" s="14"/>
+    </row>
+    <row r="21" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="B21" s="12"/>
+      <c r="C21" s="14"/>
+      <c r="D21" s="14"/>
+      <c r="E21" s="14"/>
+      <c r="F21" s="14"/>
+      <c r="G21" s="14"/>
+    </row>
+    <row r="22" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="14"/>
+      <c r="B22" s="14"/>
+      <c r="C22" s="14"/>
+      <c r="D22" s="14"/>
+      <c r="E22" s="14"/>
+      <c r="F22" s="14"/>
+      <c r="G22" s="14"/>
+    </row>
+    <row r="23" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="B23" s="14"/>
+      <c r="C23" s="14"/>
+      <c r="D23" s="14"/>
+      <c r="E23" s="14"/>
+      <c r="F23" s="14"/>
+      <c r="G23" s="14"/>
+    </row>
+    <row r="24" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="B24" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="C24" s="14"/>
+      <c r="D24" s="14"/>
+      <c r="E24" s="14"/>
+      <c r="F24" s="14"/>
+      <c r="G24" s="14"/>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A25" s="6"/>
+      <c r="B25" s="7">
+        <v>133</v>
+      </c>
+      <c r="C25" s="14"/>
+      <c r="D25" s="14"/>
+      <c r="E25" s="14"/>
+      <c r="F25" s="14"/>
+      <c r="G25" s="14"/>
+    </row>
+    <row r="26" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="B26" s="12"/>
+      <c r="C26" s="14"/>
+      <c r="D26" s="14"/>
+      <c r="E26" s="14"/>
+      <c r="F26" s="14"/>
+      <c r="G26" s="14"/>
+    </row>
+    <row r="27" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="28" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="13" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="14" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="3" t="s">
+    <row r="29" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B14" s="4" t="s">
+      <c r="B29" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="4" t="s">
+      <c r="C29" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="D14" s="4" t="s">
+      <c r="D29" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="E14" s="4" t="s">
+      <c r="E29" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="F14" s="4" t="s">
+      <c r="F29" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="G14" s="4" t="s">
+      <c r="G29" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="H14" s="5" t="s">
+      <c r="H29" s="4" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A15" s="6" t="s">
+      <c r="I29" s="15" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A30" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="B15" s="2">
+      <c r="B30" s="2">
         <v>10</v>
       </c>
-      <c r="C15" s="2"/>
-      <c r="D15" s="2"/>
-      <c r="E15" s="2"/>
-      <c r="F15" s="2"/>
-      <c r="G15" s="2"/>
-      <c r="H15" s="7"/>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A16" s="8" t="s">
+      <c r="C30" s="2"/>
+      <c r="D30" s="2"/>
+      <c r="E30" s="2"/>
+      <c r="F30" s="2"/>
+      <c r="G30" s="2"/>
+      <c r="H30" s="2"/>
+      <c r="I30" s="7"/>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A31" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="B16" s="1"/>
-      <c r="C16" s="1">
+      <c r="B31" s="1"/>
+      <c r="C31" s="1">
         <v>23</v>
       </c>
-      <c r="D16" s="1"/>
-      <c r="E16" s="1"/>
-      <c r="F16" s="1"/>
-      <c r="G16" s="1"/>
-      <c r="H16" s="9"/>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A17" s="8" t="s">
+      <c r="D31" s="1"/>
+      <c r="E31" s="1"/>
+      <c r="F31" s="1"/>
+      <c r="G31" s="1"/>
+      <c r="H31" s="1"/>
+      <c r="I31" s="9"/>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A32" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="B17" s="1"/>
-      <c r="C17" s="1"/>
-      <c r="D17" s="1">
+      <c r="B32" s="1"/>
+      <c r="C32" s="1"/>
+      <c r="D32" s="1">
         <v>50</v>
       </c>
-      <c r="E17" s="1"/>
-      <c r="F17" s="1"/>
-      <c r="G17" s="1"/>
-      <c r="H17" s="9"/>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A18" s="8" t="s">
+      <c r="E32" s="1"/>
+      <c r="F32" s="1"/>
+      <c r="G32" s="1"/>
+      <c r="H32" s="1"/>
+      <c r="I32" s="9"/>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A33" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="B18" s="1"/>
-      <c r="C18" s="1"/>
-      <c r="D18" s="1"/>
-      <c r="E18" s="1">
+      <c r="B33" s="1"/>
+      <c r="C33" s="1"/>
+      <c r="D33" s="1"/>
+      <c r="E33" s="1">
         <v>12</v>
       </c>
-      <c r="F18" s="1"/>
-      <c r="G18" s="1"/>
-      <c r="H18" s="9"/>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A19" s="8" t="s">
+      <c r="F33" s="1"/>
+      <c r="G33" s="1"/>
+      <c r="H33" s="1"/>
+      <c r="I33" s="9"/>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A34" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="B19" s="1"/>
-      <c r="C19" s="1"/>
-      <c r="D19" s="1"/>
-      <c r="E19" s="1"/>
-      <c r="F19" s="1">
+      <c r="B34" s="1"/>
+      <c r="C34" s="1"/>
+      <c r="D34" s="1"/>
+      <c r="E34" s="1"/>
+      <c r="F34" s="1">
         <v>40</v>
       </c>
-      <c r="G19" s="1"/>
-      <c r="H19" s="9"/>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A20" s="8" t="s">
+      <c r="G34" s="1"/>
+      <c r="H34" s="1"/>
+      <c r="I34" s="9"/>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A35" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="B20" s="1"/>
-      <c r="C20" s="1"/>
-      <c r="D20" s="1"/>
-      <c r="E20" s="1"/>
-      <c r="F20" s="1"/>
-      <c r="G20" s="1">
+      <c r="B35" s="1"/>
+      <c r="C35" s="1"/>
+      <c r="D35" s="1"/>
+      <c r="E35" s="1"/>
+      <c r="F35" s="1"/>
+      <c r="G35" s="1">
         <v>30</v>
       </c>
-      <c r="H20" s="9"/>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A21" s="8" t="s">
+      <c r="H35" s="1"/>
+      <c r="I35" s="9"/>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A36" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="B21" s="1"/>
-      <c r="C21" s="1"/>
-      <c r="D21" s="1"/>
-      <c r="E21" s="1"/>
-      <c r="F21" s="1"/>
-      <c r="G21" s="1"/>
-      <c r="H21" s="9">
+      <c r="B36" s="1"/>
+      <c r="C36" s="1"/>
+      <c r="D36" s="1"/>
+      <c r="E36" s="1"/>
+      <c r="F36" s="1"/>
+      <c r="G36" s="1"/>
+      <c r="H36" s="1">
         <v>25</v>
       </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A22" s="8" t="str">
-        <f>_xlfn.CONCAT("El volumen del recipiente en forma de prisma es: ",B15*C16*D17," cm cúbicos")</f>
+      <c r="I36" s="9"/>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A37" s="8" t="str">
+        <f>_xlfn.CONCAT("El volumen del recipiente en forma de prisma es: ",B30*C31*D32," cm cúbicos")</f>
         <v>El volumen del recipiente en forma de prisma es: 11500 cm cúbicos</v>
       </c>
-      <c r="B22" s="1"/>
-      <c r="C22" s="1"/>
-      <c r="D22" s="1"/>
-      <c r="E22" s="1"/>
-      <c r="F22" s="1"/>
-      <c r="G22" s="1"/>
-      <c r="H22" s="9"/>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A23" s="8" t="str">
-        <f>_xlfn.CONCAT("El volumen del recipiente en forma de cilindro es: ",PI()*POWER(E18,2)*F19," cm cúbicos")</f>
+      <c r="B37" s="1"/>
+      <c r="C37" s="1"/>
+      <c r="D37" s="1"/>
+      <c r="E37" s="1"/>
+      <c r="F37" s="1"/>
+      <c r="G37" s="1"/>
+      <c r="H37" s="1"/>
+      <c r="I37" s="9" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A38" s="8" t="str">
+        <f>_xlfn.CONCAT("El volumen del recipiente en forma de cilindro es: ",PI()*POWER(E33,2)*F34," cm cúbicos")</f>
         <v>El volumen del recipiente en forma de cilindro es: 18095,5736846772 cm cúbicos</v>
       </c>
-      <c r="B23" s="1"/>
-      <c r="C23" s="1"/>
-      <c r="D23" s="1"/>
-      <c r="E23" s="1"/>
-      <c r="F23" s="1"/>
-      <c r="G23" s="1"/>
-      <c r="H23" s="9"/>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A24" s="8" t="str">
-        <f>_xlfn.CONCAT("La cantidad de leche recogida en el recipiente en forma de prisma es: ",(B15*C16*D17)*(G20/D17)," cm cúbicos")</f>
+      <c r="B38" s="1"/>
+      <c r="C38" s="1"/>
+      <c r="D38" s="1"/>
+      <c r="E38" s="1"/>
+      <c r="F38" s="1"/>
+      <c r="G38" s="1"/>
+      <c r="H38" s="1"/>
+      <c r="I38" s="9" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A39" s="8" t="str">
+        <f>_xlfn.CONCAT("La cantidad de leche recogida en el recipiente en forma de prisma es: ",(B30*C31*D32)*(G35/D32)," cm cúbicos")</f>
         <v>La cantidad de leche recogida en el recipiente en forma de prisma es: 6900 cm cúbicos</v>
       </c>
-      <c r="B24" s="1"/>
-      <c r="C24" s="1"/>
-      <c r="D24" s="1"/>
-      <c r="E24" s="1"/>
-      <c r="F24" s="1"/>
-      <c r="G24" s="1"/>
-      <c r="H24" s="9"/>
-    </row>
-    <row r="25" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="10" t="str">
-        <f>_xlfn.CONCAT("La cantidad de leche recogida en el recipiente en forma de cilindro es: ",(PI()*POWER(E18,2)*F19)*(H21/F19)," cm cúbicos")</f>
+      <c r="B39" s="1"/>
+      <c r="C39" s="1"/>
+      <c r="D39" s="1"/>
+      <c r="E39" s="1"/>
+      <c r="F39" s="1"/>
+      <c r="G39" s="1"/>
+      <c r="H39" s="1"/>
+      <c r="I39" s="9" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="10" t="str">
+        <f>_xlfn.CONCAT("La cantidad de leche recogida en el recipiente en forma de cilindro es: ",(PI()*POWER(E33,2)*F34)*(H36/F34)," cm cúbicos")</f>
         <v>La cantidad de leche recogida en el recipiente en forma de cilindro es: 11309,7335529233 cm cúbicos</v>
       </c>
-      <c r="B25" s="11"/>
-      <c r="C25" s="11"/>
-      <c r="D25" s="11"/>
-      <c r="E25" s="11"/>
-      <c r="F25" s="11"/>
-      <c r="G25" s="11"/>
-      <c r="H25" s="12"/>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="C30" s="15"/>
+      <c r="B40" s="11"/>
+      <c r="C40" s="11"/>
+      <c r="D40" s="11"/>
+      <c r="E40" s="11"/>
+      <c r="F40" s="11"/>
+      <c r="G40" s="11"/>
+      <c r="H40" s="11"/>
+      <c r="I40" s="12" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="42" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="13" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="B43" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C43" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D43" s="5" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A44" s="6"/>
+      <c r="B44" s="2">
+        <v>10</v>
+      </c>
+      <c r="C44" s="2">
+        <v>23</v>
+      </c>
+      <c r="D44" s="7">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="10">
+        <f>B44*C44*D44</f>
+        <v>11500</v>
+      </c>
+      <c r="B45" s="11"/>
+      <c r="C45" s="20"/>
+      <c r="D45" s="12"/>
+    </row>
+    <row r="46" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="47" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="13" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="B48" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C48" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A49" s="6"/>
+      <c r="B49" s="2">
+        <v>12</v>
+      </c>
+      <c r="C49" s="7">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="21">
+        <f>PI()*POWER(B49,2)*C49</f>
+        <v>18095.573684677209</v>
+      </c>
+      <c r="B50" s="11"/>
+      <c r="C50" s="12"/>
+    </row>
+    <row r="51" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="52" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="13" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A53" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="B53" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C53" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D53" s="15" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A54" s="6"/>
+      <c r="B54" s="2">
+        <v>50</v>
+      </c>
+      <c r="C54" s="2">
+        <v>30</v>
+      </c>
+      <c r="D54" s="7" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A55" s="10">
+        <f>A45*(C54/B54)</f>
+        <v>6900</v>
+      </c>
+      <c r="B55" s="11"/>
+      <c r="C55" s="11"/>
+      <c r="D55" s="12"/>
+    </row>
+    <row r="56" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="57" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A57" s="13" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A58" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="B58" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C58" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D58" s="15" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A59" s="6"/>
+      <c r="B59" s="2">
+        <v>40</v>
+      </c>
+      <c r="C59" s="2">
+        <v>25</v>
+      </c>
+      <c r="D59" s="7" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A60" s="21">
+        <f>A50*(C59/B59)</f>
+        <v>11309.733552923255</v>
+      </c>
+      <c r="B60" s="11"/>
+      <c r="C60" s="11"/>
+      <c r="D60" s="12"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
